--- a/令和8年度収集カレンダー.xlsx
+++ b/令和8年度収集カレンダー.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82378E8-C8C6-8C46-8E9D-52DEBA14ABD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4540" yWindow="600" windowWidth="28200" windowHeight="19880" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4540" yWindow="600" windowWidth="28200" windowHeight="19880" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="４月" sheetId="1" r:id="rId1"/>
